--- a/examples/Myth and Legend.h3m/prt/0000.xlsx
+++ b/examples/Myth and Legend.h3m/prt/0000.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24334"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D95EA866-4BFF-4EC7-B648-FADACAD88BDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DF763DD-EED1-47F9-AB0E-4FD1718BB6E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3072" yWindow="96" windowWidth="25920" windowHeight="16560" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9408" yWindow="3504" windowWidth="25920" windowHeight="16560" tabRatio="792" firstSheet="5" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Артефакты" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,30 @@
     <sheet name="Опыт" sheetId="24" r:id="rId24"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Артефакты!$A$1:$M$145</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Банки!$A$1:$J$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="20" hidden="1">'Все Арты'!$A$1:$P$186</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="21" hidden="1">'Все Заклы'!$A$1:$N$463</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="22" hidden="1">'Все Навыки'!$A$1:$I$30</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">Гарнизоны!$A$1:$I$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="18" hidden="1">Герои!$A$1:$O$157</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="19" hidden="1">Города!$A$1:$N$102</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">Заклинания!$A$1:$I$43</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Лагеря Беженцев'!$A$1:$H$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Монстры!$A$1:$M$239</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">Навыки!$A$1:$F$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="15" hidden="1">Объекты!$A$1:$F$28</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="23" hidden="1">Опыт!$A$1:$O$576</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">Провидцы!$A$1:$G$23</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">Ресурсы!$A$1:$I$486</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">Рынки!$A$1:$J$29</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'События и Ящики Пандоры'!$A$1:$S$102</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">'События-Таймеры'!$A$1:$L$181</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'Стражи Прохода'!$A$1:$F$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">Сундуки!$A$1:$J$285</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="16" hidden="1">Топология!$A$1:$H$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">Тюрьмы!$A$1:$P$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Ученые!$A$1:$G$12</definedName>
   </definedNames>
   <calcPr calcId="124519"/>
   <extLst>
@@ -7466,6 +7489,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:M145" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -7554,6 +7578,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:H3" xr:uid="{00000000-0001-0000-0900-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -8360,6 +8385,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:J29" xr:uid="{00000000-0001-0000-0A00-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -8368,6 +8394,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <dimension ref="A1:G23"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="5" max="5" width="57.21875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="26.6640625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
@@ -8803,6 +8833,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:G23" xr:uid="{00000000-0001-0000-0B00-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -9020,6 +9051,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:F12" xr:uid="{00000000-0001-0000-0C00-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -9160,6 +9192,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:I5" xr:uid="{00000000-0001-0000-0D00-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -9469,6 +9502,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:P7" xr:uid="{00000000-0001-0000-0E00-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -9979,6 +10013,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:F28" xr:uid="{00000000-0001-0000-0F00-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -10315,6 +10350,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:H16" xr:uid="{00000000-0001-0000-1000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -14065,6 +14101,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:L181" xr:uid="{00000000-0001-0000-1100-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -18778,6 +18815,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:O157" xr:uid="{00000000-0001-0000-1200-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -26478,6 +26516,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:M239" xr:uid="{00000000-0001-0000-0100-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -34099,6 +34138,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:P186" xr:uid="{00000000-0001-0000-1400-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -44896,6 +44936,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:N463" xr:uid="{00000000-0001-0000-1500-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -45527,6 +45568,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:I30" xr:uid="{00000000-0001-0000-1600-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -59829,6 +59871,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:O576" xr:uid="{00000000-0001-0000-1700-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -60094,6 +60137,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:J9" xr:uid="{00000000-0001-0000-0200-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -62312,6 +62356,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:S102" xr:uid="{00000000-0001-0000-0300-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -62532,6 +62577,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:G12" xr:uid="{00000000-0001-0000-0400-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -72361,6 +72407,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:I486" xr:uid="{00000000-0001-0000-0500-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -78953,6 +79000,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:J285" xr:uid="{00000000-0001-0000-0600-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -79964,6 +80012,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:I43" xr:uid="{00000000-0001-0000-0700-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -80294,6 +80343,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:F16" xr:uid="{00000000-0001-0000-0800-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/examples/Myth and Legend.h3m/prt/0000.xlsx
+++ b/examples/Myth and Legend.h3m/prt/0000.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24334"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92ADAED5-8325-4FEC-91C9-C93B72D6934B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85CF10FE-5DE8-401A-88E5-D25B66E2C40E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4800" yWindow="0" windowWidth="25920" windowHeight="16560" firstSheet="14" activeTab="20" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" firstSheet="12" activeTab="23" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Артефакты" sheetId="1" r:id="rId1"/>
@@ -119,70 +119,70 @@
     <t>Большой</t>
   </si>
   <si>
-    <t>Сапоги-скороходы</t>
+    <t>Сапоги-Скороходы</t>
   </si>
   <si>
     <t>Малый</t>
   </si>
   <si>
-    <t>Корона верховного волхва</t>
-  </si>
-  <si>
-    <t>Доспехи из ребер</t>
-  </si>
-  <si>
-    <t>Доспехи проклятого</t>
-  </si>
-  <si>
-    <t>Талисман маны</t>
+    <t>Корона Главного Мага</t>
+  </si>
+  <si>
+    <t>Ребра</t>
+  </si>
+  <si>
+    <t>Доспехи Проклятого</t>
+  </si>
+  <si>
+    <t>Талисман Маны</t>
   </si>
   <si>
     <t>Сокровище</t>
   </si>
   <si>
-    <t>Колодец волшебника</t>
-  </si>
-  <si>
-    <t>Шлем-череп</t>
+    <t>Колодец Волшебника</t>
+  </si>
+  <si>
+    <t>Шлем-Череп</t>
   </si>
   <si>
     <t>Склеп</t>
   </si>
   <si>
-    <t>Значок смелости</t>
-  </si>
-  <si>
-    <t>Скелет 20, Живой мертвец 20, Страж 10, Вампир 10</t>
-  </si>
-  <si>
-    <t>Накидка скорости</t>
-  </si>
-  <si>
-    <t>Дух уныния</t>
-  </si>
-  <si>
-    <t>Туловище легиона</t>
-  </si>
-  <si>
-    <t>Статуя легиона</t>
-  </si>
-  <si>
-    <t>Эльфийский лук из вишневого дерева</t>
+    <t>Значок Смелости</t>
+  </si>
+  <si>
+    <t>Скелет 20, Живой Мертвец 20, Страж 10, Вампир 10</t>
+  </si>
+  <si>
+    <t>Накидка Скорости</t>
+  </si>
+  <si>
+    <t>Дух Уныния</t>
+  </si>
+  <si>
+    <t>Туловище Легиона</t>
+  </si>
+  <si>
+    <t>Статуя Легиона</t>
+  </si>
+  <si>
+    <t>Лук из Вишневого Дерева Эльфов</t>
   </si>
   <si>
     <t>Лук Снайпера</t>
   </si>
   <si>
-    <t>Карты пророчества</t>
-  </si>
-  <si>
-    <t>Ожерелье стремительности</t>
-  </si>
-  <si>
-    <t>Неиссякаемая мошна золота</t>
-  </si>
-  <si>
-    <t>Щит тоскующих мертвецов</t>
+    <t>Карты Пророчества</t>
+  </si>
+  <si>
+    <t>Ожерелье Стремительности</t>
+  </si>
+  <si>
+    <t>Неиссякаемая Мошна Золота</t>
+  </si>
+  <si>
+    <t>Щит Тоскующих Мертвецов</t>
   </si>
   <si>
     <t>Кольчуга Великого Василиска</t>
@@ -191,28 +191,28 @@
     <t>море</t>
   </si>
   <si>
-    <t>Ветхий корабль</t>
-  </si>
-  <si>
-    <t>Шлем белого Единорога</t>
-  </si>
-  <si>
-    <t>Элементаль воды 30</t>
-  </si>
-  <si>
-    <t>Могила воина</t>
-  </si>
-  <si>
-    <t>Языки пламени Красного Дракона</t>
+    <t>Ветхий Корабль</t>
+  </si>
+  <si>
+    <t>Шлем Белого Единорога</t>
+  </si>
+  <si>
+    <t>Элементаль Воды 30</t>
+  </si>
+  <si>
+    <t>Могила Воина</t>
+  </si>
+  <si>
+    <t>Языки Пламени Красного Дракона</t>
   </si>
   <si>
     <t>Мощь отца Драконов</t>
   </si>
   <si>
-    <t>Утопия драконов</t>
-  </si>
-  <si>
-    <t>Ожерелье божественной благодати</t>
+    <t>Утопия Драконов</t>
+  </si>
+  <si>
+    <t>Ожерелье Божественной Благодати</t>
   </si>
   <si>
     <t>Реликвия</t>
@@ -221,79 +221,79 @@
     <t>Альянс Ангелов</t>
   </si>
   <si>
-    <t>Зеленый дракон 8, Красный дракон 5, Золотой дракон 2, Черный дракон 1</t>
-  </si>
-  <si>
-    <t>Голова легиона</t>
-  </si>
-  <si>
-    <t>Черный клинок мертвого рыцаря</t>
-  </si>
-  <si>
-    <t>Кольцо дипломата</t>
-  </si>
-  <si>
-    <t>Щит короля Гноллов</t>
-  </si>
-  <si>
-    <t>Потерпевший кораблекрушение</t>
-  </si>
-  <si>
-    <t>Неиссякаемая склянка ртути</t>
+    <t>Зеленый Дракон 8, Красный Дракон 5, Золотой Дракон 2, Черный Дракон 1</t>
+  </si>
+  <si>
+    <t>Голова Легиона</t>
+  </si>
+  <si>
+    <t>Блэкшард Мертвого Рыцаря</t>
+  </si>
+  <si>
+    <t>Кольцо Дипломата</t>
+  </si>
+  <si>
+    <t>Щит Короля Гноллов</t>
+  </si>
+  <si>
+    <t>Потерпевший Кораблекрушение</t>
+  </si>
+  <si>
+    <t>Неиссякаемая Склянка Ртути</t>
   </si>
   <si>
     <t>Рог изобилия</t>
   </si>
   <si>
-    <t>Наколенники из Драконьей кости</t>
-  </si>
-  <si>
-    <t>Ожерелье морского проведения</t>
-  </si>
-  <si>
-    <t>Шляпа адмирала</t>
-  </si>
-  <si>
-    <t>Плащ бесконечных кристаллов</t>
-  </si>
-  <si>
-    <t>Магическое кольцо</t>
+    <t>Наколенники из Драконьей Кости</t>
+  </si>
+  <si>
+    <t>Ожерелье Морского Проведения</t>
+  </si>
+  <si>
+    <t>Шляпа Адмирала</t>
+  </si>
+  <si>
+    <t>Плащ Бесконечных Кристаллов</t>
+  </si>
+  <si>
+    <t>Магическое Кольцо</t>
   </si>
   <si>
     <t>Кольцо Мага</t>
   </si>
   <si>
-    <t>Голубка удачи</t>
+    <t>Голубка Удачи</t>
   </si>
   <si>
     <t>Секира Кентавра</t>
   </si>
   <si>
-    <t>Магическое ожерелье</t>
-  </si>
-  <si>
-    <t>Неиссякаемая сума золота</t>
-  </si>
-  <si>
-    <t>Джинн 10</t>
-  </si>
-  <si>
-    <t>Бесстрашный хранитель</t>
-  </si>
-  <si>
-    <t>Ноги легиона</t>
-  </si>
-  <si>
-    <t>Поясница легиона</t>
-  </si>
-  <si>
-    <t>Великий Гноллий кистень</t>
-  </si>
-  <si>
-    <t>Магические доспехи</t>
-  </si>
-  <si>
-    <t>Символ знаний</t>
+    <t>Магический Ошейник</t>
+  </si>
+  <si>
+    <t>Неиссякаемая Сума Золота</t>
+  </si>
+  <si>
+    <t>Джин 10</t>
+  </si>
+  <si>
+    <t>Бесстрашный Хранитель</t>
+  </si>
+  <si>
+    <t>Ноги Легиона</t>
+  </si>
+  <si>
+    <t>Поясница Легиона</t>
+  </si>
+  <si>
+    <t>Великий Гномий Кистень</t>
+  </si>
+  <si>
+    <t>Магические Доспехи</t>
+  </si>
+  <si>
+    <t>Символ Знаний</t>
   </si>
   <si>
     <t>Кораблекрушение</t>
@@ -302,133 +302,133 @@
     <t>Страж 15</t>
   </si>
   <si>
-    <t>Сфера небесного свода</t>
-  </si>
-  <si>
-    <t>Брелок свободы</t>
-  </si>
-  <si>
-    <t>Адский меч</t>
-  </si>
-  <si>
-    <t>Сандалии святых</t>
-  </si>
-  <si>
-    <t>Плащ отречения</t>
-  </si>
-  <si>
-    <t>Неистощимая подвода леса</t>
-  </si>
-  <si>
-    <t>Тетива из волос гривы Единорога</t>
-  </si>
-  <si>
-    <t>Щит стража</t>
+    <t>Сфера Небесного Свода</t>
+  </si>
+  <si>
+    <t>Брелок Свободы</t>
+  </si>
+  <si>
+    <t>Адский Меч</t>
+  </si>
+  <si>
+    <t>Сандалии Святых</t>
+  </si>
+  <si>
+    <t>Плащ Отречения</t>
+  </si>
+  <si>
+    <t>Неистощимая Подвода Леса</t>
+  </si>
+  <si>
+    <t>Тетива из Волоса Гривы Единорога</t>
+  </si>
+  <si>
+    <t>Щит Часового</t>
   </si>
   <si>
     <t>Грохот Титана</t>
   </si>
   <si>
-    <t>Нагрудник из окаменелого дерева</t>
-  </si>
-  <si>
-    <t>Герб доблести</t>
-  </si>
-  <si>
-    <t>Птица познания</t>
-  </si>
-  <si>
-    <t>Перчатки всадника</t>
-  </si>
-  <si>
-    <t>Брелок ясновидения</t>
-  </si>
-  <si>
-    <t>Магическая медаль маны</t>
-  </si>
-  <si>
-    <t>Неподвижный глаз Дракона</t>
-  </si>
-  <si>
-    <t>Магическая накидка</t>
-  </si>
-  <si>
-    <t>Шлем хаоса</t>
-  </si>
-  <si>
-    <t>Щит проклятых</t>
-  </si>
-  <si>
-    <t>Плащ из Драконьих крыльев</t>
-  </si>
-  <si>
-    <t>Золотой лук</t>
-  </si>
-  <si>
-    <t>Знак отваги</t>
-  </si>
-  <si>
-    <t>Щит гномьих Героев</t>
+    <t>Нагрудник из Окаменелого Дерева</t>
+  </si>
+  <si>
+    <t>Герб Доблести</t>
+  </si>
+  <si>
+    <t>Птица Познания</t>
+  </si>
+  <si>
+    <t>Перчатки Всадника</t>
+  </si>
+  <si>
+    <t>Брелок Ясновидения</t>
+  </si>
+  <si>
+    <t>Магическая Медаль Маны</t>
+  </si>
+  <si>
+    <t>Неподвижный Глаз Дракона</t>
+  </si>
+  <si>
+    <t>Магическая Накидка</t>
+  </si>
+  <si>
+    <t>Шлем Хаоса</t>
+  </si>
+  <si>
+    <t>Щит Проклятых</t>
+  </si>
+  <si>
+    <t>Плащ из Драконьих Крыльев</t>
+  </si>
+  <si>
+    <t>Золотой Лук</t>
+  </si>
+  <si>
+    <t>Знак Отваги</t>
+  </si>
+  <si>
+    <t>Щит Гномьих Богов</t>
   </si>
   <si>
     <t>Мантия Вампира</t>
   </si>
   <si>
-    <t>Плащ короля нежити</t>
-  </si>
-  <si>
-    <t>Кольцо жизненной силы</t>
-  </si>
-  <si>
-    <t>Эликсир жизни</t>
-  </si>
-  <si>
-    <t>Амулет маны</t>
-  </si>
-  <si>
-    <t>Подзорная труба</t>
-  </si>
-  <si>
-    <t>Неистощимая подвода с рудой</t>
-  </si>
-  <si>
-    <t>Телескоп</t>
-  </si>
-  <si>
-    <t>Брелок бесстрастия</t>
-  </si>
-  <si>
-    <t>Клевер удачи</t>
-  </si>
-  <si>
-    <t>Кольцо жизни</t>
-  </si>
-  <si>
-    <t>Застывший глаз Дракона</t>
-  </si>
-  <si>
-    <t>Брелок смерти</t>
-  </si>
-  <si>
-    <t>Амулет гробовщика</t>
-  </si>
-  <si>
-    <t>Сфера проливного дождя</t>
-  </si>
-  <si>
-    <t>Священный брелок</t>
-  </si>
-  <si>
-    <t>Карающая дубина Огра</t>
-  </si>
-  <si>
-    <t>Песочные часы недоброго часа</t>
-  </si>
-  <si>
-    <t>Руки легиона</t>
-  </si>
-  <si>
-    <t>Шар постоянства</t>
+    <t>Плащ Короля Нечисти</t>
+  </si>
+  <si>
+    <t>Кольцо Жизненной Силы</t>
+  </si>
+  <si>
+    <t>Эликсир Жизни</t>
+  </si>
+  <si>
+    <t>Амулет Маны</t>
+  </si>
+  <si>
+    <t>Подзорная Труба</t>
+  </si>
+  <si>
+    <t>Неистощимая Подвода с Рудой</t>
+  </si>
+  <si>
+    <t>Зеркало</t>
+  </si>
+  <si>
+    <t>Брелок Бесстрастия</t>
+  </si>
+  <si>
+    <t>Клевер Удачи</t>
+  </si>
+  <si>
+    <t>Кольцо Жизни</t>
+  </si>
+  <si>
+    <t>Застывшей Глаз Дракона</t>
+  </si>
+  <si>
+    <t>Брелок Смерти</t>
+  </si>
+  <si>
+    <t>Амулет Гробовщика</t>
+  </si>
+  <si>
+    <t>Сфера Проливного Дождя</t>
+  </si>
+  <si>
+    <t>Священный Брелок</t>
+  </si>
+  <si>
+    <t>Карающая Дубина Орга</t>
+  </si>
+  <si>
+    <t>Песочные Часы Недоброго Часа</t>
+  </si>
+  <si>
+    <t>Руки Легиона</t>
+  </si>
+  <si>
+    <t>Шар Постоянства</t>
   </si>
   <si>
     <t>Телега</t>
@@ -437,7 +437,7 @@
     <t>G2</t>
   </si>
   <si>
-    <t>Склянка жизненой силы</t>
+    <t>Склянка Жизненной Силы</t>
   </si>
   <si>
     <t>M5</t>
@@ -446,25 +446,25 @@
     <t>Труп</t>
   </si>
   <si>
-    <t>Сфера бушующего огня</t>
-  </si>
-  <si>
-    <t>Сфера илистого озера</t>
-  </si>
-  <si>
-    <t>Оковы войны</t>
-  </si>
-  <si>
-    <t>Брелок отрицательности</t>
-  </si>
-  <si>
-    <t>Кольцо странника</t>
-  </si>
-  <si>
-    <t>Вечное кольцо серы</t>
-  </si>
-  <si>
-    <t>Брелок смелости</t>
+    <t>Сфера Бушующего Огня</t>
+  </si>
+  <si>
+    <t>Сфера Илистого Озера</t>
+  </si>
+  <si>
+    <t>Оковы Войны</t>
+  </si>
+  <si>
+    <t>Брелок Отрицательности</t>
+  </si>
+  <si>
+    <t>Кольцо Странника</t>
+  </si>
+  <si>
+    <t>Вечное Кольцо Серы</t>
+  </si>
+  <si>
+    <t>Брелок Смелости</t>
   </si>
   <si>
     <t>Монстр</t>
@@ -482,19 +482,19 @@
     <t>Прирост</t>
   </si>
   <si>
-    <t>Королева медуза</t>
+    <t>Королева Медуза</t>
   </si>
   <si>
     <t>Да</t>
   </si>
   <si>
-    <t>Магический элементаль</t>
-  </si>
-  <si>
-    <t>Змий-дракон</t>
-  </si>
-  <si>
-    <t>Дендроид охранник</t>
+    <t>Магический Элементаль</t>
+  </si>
+  <si>
+    <t>Стрекоза</t>
+  </si>
+  <si>
+    <t>Дендроид Охранник</t>
   </si>
   <si>
     <t>Орк</t>
@@ -503,25 +503,25 @@
     <t>Налетчик</t>
   </si>
   <si>
-    <t>Элементаль воды</t>
-  </si>
-  <si>
-    <t>Ящер-воин</t>
-  </si>
-  <si>
-    <t>Змий</t>
-  </si>
-  <si>
-    <t>Ледяной элементаль</t>
-  </si>
-  <si>
-    <t>Адская гончая</t>
+    <t>Элементаль Воды</t>
+  </si>
+  <si>
+    <t>Ящер-Воин</t>
+  </si>
+  <si>
+    <t>Змей</t>
+  </si>
+  <si>
+    <t>Ледяной Элементаль</t>
+  </si>
+  <si>
+    <t>Адская Гончая</t>
   </si>
   <si>
     <t>Ящер</t>
   </si>
   <si>
-    <t>Каменный голем</t>
+    <t>Каменный Голем</t>
   </si>
   <si>
     <t>Вор</t>
@@ -536,13 +536,13 @@
     <t>Гарпия</t>
   </si>
   <si>
-    <t>Тяжелый арбалетчик</t>
-  </si>
-  <si>
-    <t>Орк-вождь</t>
-  </si>
-  <si>
-    <t>Огненный элементаль</t>
+    <t>Стрелок</t>
+  </si>
+  <si>
+    <t>Орк-Вождь</t>
+  </si>
+  <si>
+    <t>Огненный Элементаль</t>
   </si>
   <si>
     <t>Крестоносец</t>
@@ -551,16 +551,16 @@
     <t>Демон</t>
   </si>
   <si>
-    <t>Злой глаз</t>
+    <t>Дурной Глаз</t>
   </si>
   <si>
     <t>Мумия</t>
   </si>
   <si>
-    <t>Лесной эльф</t>
-  </si>
-  <si>
-    <t>Вампир лорд</t>
+    <t>Лесной Ельф</t>
+  </si>
+  <si>
+    <t>Вампир Лорд</t>
   </si>
   <si>
     <t>Гидра</t>
@@ -569,7 +569,7 @@
     <t>Вампир</t>
   </si>
   <si>
-    <t>Элементаль земли</t>
+    <t>Элементаль Земли</t>
   </si>
   <si>
     <t>Циклоп</t>
@@ -578,19 +578,19 @@
     <t>Копейщик</t>
   </si>
   <si>
-    <t>Воздушный элементаль</t>
-  </si>
-  <si>
-    <t>Капитан кентавров</t>
+    <t>Воздушный Элементаль</t>
+  </si>
+  <si>
+    <t>Капитан Кентавров</t>
   </si>
   <si>
     <t>Грифон</t>
   </si>
   <si>
-    <t>Арбалетчик</t>
-  </si>
-  <si>
-    <t>Живой мертвец</t>
+    <t>Лучник</t>
+  </si>
+  <si>
+    <t>Живой Мертвец</t>
   </si>
   <si>
     <t>Фея</t>
@@ -599,34 +599,34 @@
     <t>Горгона</t>
   </si>
   <si>
-    <t>Архи-маг</t>
+    <t>Архи-Маг</t>
   </si>
   <si>
     <t>Фанатик</t>
   </si>
   <si>
-    <t>Серебряный пегас</t>
+    <t>Серебрянный Пегас</t>
   </si>
   <si>
     <t>Зомби</t>
   </si>
   <si>
-    <t>Огр-шаман</t>
-  </si>
-  <si>
-    <t>Благородный эльф</t>
+    <t>Людоед Маг</t>
+  </si>
+  <si>
+    <t>Великий Эльф</t>
   </si>
   <si>
     <t>Кентавр</t>
   </si>
   <si>
-    <t>Королевский грифон</t>
-  </si>
-  <si>
-    <t>Гремлин</t>
-  </si>
-  <si>
-    <t>Боевой гном</t>
+    <t>Королевский Грифон</t>
+  </si>
+  <si>
+    <t>Гремли</t>
+  </si>
+  <si>
+    <t>Боевой Гном</t>
   </si>
   <si>
     <t>Единорог</t>
@@ -638,52 +638,52 @@
     <t>Нет</t>
   </si>
   <si>
-    <t>Великий василиск</t>
-  </si>
-  <si>
-    <t>Бехолдер</t>
-  </si>
-  <si>
-    <t>Магог</t>
+    <t>Великий Василиск</t>
+  </si>
+  <si>
+    <t>Созерцатель</t>
+  </si>
+  <si>
+    <t>Магога</t>
   </si>
   <si>
     <t>Гоблин</t>
   </si>
   <si>
-    <t>Гнолл-мародер</t>
-  </si>
-  <si>
-    <t>Обсидиановая горгулья</t>
-  </si>
-  <si>
-    <t>Маленькая фея</t>
-  </si>
-  <si>
-    <t>Порождение зла</t>
+    <t>Гнолл-Мародер</t>
+  </si>
+  <si>
+    <t>Обсидиановая Горгулья</t>
+  </si>
+  <si>
+    <t>Маленькая Фея</t>
+  </si>
+  <si>
+    <t>Порождение Зла</t>
   </si>
   <si>
     <t>Цербер</t>
   </si>
   <si>
-    <t>Дендроид солдат</t>
-  </si>
-  <si>
-    <t>Мечник</t>
-  </si>
-  <si>
-    <t>Элементаль шторма</t>
-  </si>
-  <si>
-    <t>Черт</t>
-  </si>
-  <si>
-    <t>Гарпия-ведьма</t>
+    <t>Дендроид Солдат</t>
+  </si>
+  <si>
+    <t>Рыцарь</t>
+  </si>
+  <si>
+    <t>Элементаль Шторма</t>
+  </si>
+  <si>
+    <t>Чёрт</t>
+  </si>
+  <si>
+    <t>Гарпия-Ведьма</t>
   </si>
   <si>
     <t>Каменная Горгулья</t>
   </si>
   <si>
-    <t>Орк на кабане</t>
+    <t>Кабан</t>
   </si>
   <si>
     <t>Кочевник</t>
@@ -698,10 +698,10 @@
     <t>Скелет</t>
   </si>
   <si>
-    <t>Золотой голем</t>
-  </si>
-  <si>
-    <t>Красный дракон</t>
+    <t>Золотой Голем</t>
+  </si>
+  <si>
+    <t>Красный Дракон</t>
   </si>
   <si>
     <t>Латы Титана</t>
@@ -713,34 +713,34 @@
     <t>Минотавр</t>
   </si>
   <si>
-    <t>Рыцарь смерти</t>
+    <t>Рыцарь Смерти</t>
   </si>
   <si>
     <t>Нага</t>
   </si>
   <si>
-    <t>Могущественный лич</t>
-  </si>
-  <si>
-    <t>Фолиант магии воздуха</t>
-  </si>
-  <si>
-    <t>Дракон-привидение</t>
-  </si>
-  <si>
-    <t>Воин скелет</t>
+    <t>Могущественный Лич</t>
+  </si>
+  <si>
+    <t>Книга Магии Воздуха</t>
+  </si>
+  <si>
+    <t>Дракон-Привидение</t>
+  </si>
+  <si>
+    <t>Воин Скелет</t>
   </si>
   <si>
     <t>Лич</t>
   </si>
   <si>
-    <t>Мастер-джинн</t>
+    <t>Мастер-Джин</t>
   </si>
   <si>
     <t>Чемпион</t>
   </si>
   <si>
-    <t>Костяной дракон</t>
+    <t>Костяной Дракон</t>
   </si>
   <si>
     <t>Алебардщик</t>
@@ -761,7 +761,7 @@
     <t>Василиск</t>
   </si>
   <si>
-    <t>Джинн</t>
+    <t>Джин</t>
   </si>
   <si>
     <t>Маг</t>
@@ -779,64 +779,64 @@
     <t>G10</t>
   </si>
   <si>
-    <t>Энергетический элементаль</t>
+    <t>Энергетический Элементаль</t>
   </si>
   <si>
     <t>Монах</t>
   </si>
   <si>
-    <t>Король минотавр</t>
+    <t>Король Минотавр</t>
   </si>
   <si>
     <t>Хоббит</t>
   </si>
   <si>
-    <t>Элементаль магмы</t>
-  </si>
-  <si>
-    <t>Стальной голем</t>
-  </si>
-  <si>
-    <t>Банк Наг</t>
-  </si>
-  <si>
-    <t>Нага 12, Королева нага 3</t>
+    <t>Элементаль Магмы</t>
+  </si>
+  <si>
+    <t>Стальной Голем</t>
+  </si>
+  <si>
+    <t>Нага Банк</t>
+  </si>
+  <si>
+    <t>Нага 12, Королева Нага 3</t>
   </si>
   <si>
     <t>G12</t>
   </si>
   <si>
-    <t>Улей змиев</t>
-  </si>
-  <si>
-    <t>Змий-дракон 45</t>
+    <t>Улей Змиев</t>
+  </si>
+  <si>
+    <t>Стрекоза 45</t>
   </si>
   <si>
     <t>Виверн 6</t>
   </si>
   <si>
-    <t>Хранилище медуз</t>
+    <t>Хранилище Медуз</t>
   </si>
   <si>
     <t>Медуза 50</t>
   </si>
   <si>
-    <t>Сокровищница гномов</t>
-  </si>
-  <si>
-    <t>Гном 40, Боевой гном 10</t>
+    <t>Сокровищница Гномов</t>
+  </si>
+  <si>
+    <t>Гном 40, Боевой Гном 10</t>
   </si>
   <si>
     <t>C2</t>
   </si>
   <si>
-    <t>Медуза 32, Королева медуза 8</t>
+    <t>Медуза 32, Королева Медуза 8</t>
   </si>
   <si>
     <t>S8</t>
   </si>
   <si>
-    <t>Склады циклопов</t>
+    <t>Склады Циклопов</t>
   </si>
   <si>
     <t>Циклоп 40</t>
@@ -887,7 +887,7 @@
     <t>C-5, G-5</t>
   </si>
   <si>
-    <t>Алебардщик 10, Капитан кентавров 10, Мастер-гремлин 10, Черт 10, Адский троглодит 10, Хобгоблин 10, Гнолл-мародер 10</t>
+    <t>Алебардщик 10, Капитан Кентавров 10, Мастер-Гремлин 10, Чёрт 10, Адский Троглодит 10, Хобгоблин 10, Гнолл-Мародер 10</t>
   </si>
   <si>
     <t>+2</t>
@@ -914,7 +914,7 @@
     <t>C5, G5</t>
   </si>
   <si>
-    <t>Шлем божественного просвещения</t>
+    <t>Шлем Божественного Просвещения</t>
   </si>
   <si>
     <t>G-5</t>
@@ -929,10 +929,10 @@
     <t>-2</t>
   </si>
   <si>
-    <t>Красный, Синий, Коричневый, Зеленый, Оранжевый, Пурпурный, Бирюзовый, Розовый</t>
-  </si>
-  <si>
-    <t>Защита</t>
+    <t>Красный, Синий, Коричневый, Зеленый, Оранжевый, Багровый, Чайный, Розовый</t>
+  </si>
+  <si>
+    <t>Доспехи</t>
   </si>
   <si>
     <t>Интеллект</t>
@@ -947,10 +947,10 @@
     <t>Нападение</t>
   </si>
   <si>
-    <t>Огненный шар</t>
-  </si>
-  <si>
-    <t>Стена огня</t>
+    <t>Огненный Шар</t>
+  </si>
+  <si>
+    <t>Стена Огня</t>
   </si>
   <si>
     <t>P+1</t>
@@ -971,7 +971,7 @@
     <t>S3</t>
   </si>
   <si>
-    <t>Кострище покинутого лагеря</t>
+    <t>Бивачный Костер</t>
   </si>
   <si>
     <t>O10</t>
@@ -1022,7 +1022,7 @@
     <t>W8</t>
   </si>
   <si>
-    <t>Чей-то погреб</t>
+    <t>Прислониться к</t>
   </si>
   <si>
     <t>G3</t>
@@ -1061,28 +1061,28 @@
     <t>C4</t>
   </si>
   <si>
-    <t>Королевский грифон 6, Огненная птица 3</t>
-  </si>
-  <si>
-    <t>Лазурный дракон 1</t>
-  </si>
-  <si>
-    <t>Сундук с сокровищами</t>
-  </si>
-  <si>
-    <t>Святыня магического жеста</t>
+    <t>Королевский Грифон 6, Огненная Птица 3</t>
+  </si>
+  <si>
+    <t>Лазурный Дракон 1</t>
+  </si>
+  <si>
+    <t>Сундук Сокровищ</t>
+  </si>
+  <si>
+    <t>Святыня Магического Жеста</t>
   </si>
   <si>
     <t>Устранение преград</t>
   </si>
   <si>
-    <t>Святыня магической мысли</t>
+    <t>Святыня Магической Мысли</t>
   </si>
   <si>
     <t>Кольцо холода</t>
   </si>
   <si>
-    <t>Святыня магического воплощения</t>
+    <t>Святыня Магического Воплощения</t>
   </si>
   <si>
     <t>Проклятье</t>
@@ -1115,7 +1115,7 @@
     <t>Слабость</t>
   </si>
   <si>
-    <t>Волна смерти</t>
+    <t>Волна Смерти</t>
   </si>
   <si>
     <t>Защита от воздуха</t>
@@ -1139,7 +1139,7 @@
     <t>Анти-Магия</t>
   </si>
   <si>
-    <t>Вызвать корабль</t>
+    <t>Вызвать Корабль</t>
   </si>
   <si>
     <t>Затопить корабль</t>
@@ -1148,7 +1148,7 @@
     <t>Телепорт</t>
   </si>
   <si>
-    <t>Просмотр воздуха</t>
+    <t>Просмотр Воздуха</t>
   </si>
   <si>
     <t>Разрушающий луч</t>
@@ -1181,10 +1181,10 @@
     <t>Земляной Элементаль</t>
   </si>
   <si>
-    <t>Золотой голем 40, Алмазный голем 20</t>
-  </si>
-  <si>
-    <t>Уничтожить нечисть</t>
+    <t>Золотой Голем 40, Алмазный Голем 20</t>
+  </si>
+  <si>
+    <t>Уничтожить Нечисть</t>
   </si>
   <si>
     <t>Ледяная молния</t>
@@ -1196,7 +1196,7 @@
     <t>Навык</t>
   </si>
   <si>
-    <t>Хижина ведьмы</t>
+    <t>Хижина Ведьмы</t>
   </si>
   <si>
     <t>Тактика</t>
@@ -1217,7 +1217,7 @@
     <t>Логистика</t>
   </si>
   <si>
-    <t>Поиск пути</t>
+    <t>Поиск Пути</t>
   </si>
   <si>
     <t>Первая помощь</t>
@@ -1226,19 +1226,19 @@
     <t>Мудрость</t>
   </si>
   <si>
-    <t>Обучаемость</t>
-  </si>
-  <si>
-    <t>Артиллерия, Меткость, Воздух, Нападение</t>
+    <t>Обучение</t>
+  </si>
+  <si>
+    <t>Артиллерия, Стрельба, Воздух, Нападение</t>
   </si>
   <si>
     <t>Разведка</t>
   </si>
   <si>
-    <t>Лагерь беженцев</t>
-  </si>
-  <si>
-    <t>Зеленый дракон</t>
+    <t>Лагерь Беженцов</t>
+  </si>
+  <si>
+    <t>Зеленый Дракон</t>
   </si>
   <si>
     <t>Цена на Черном Рынке</t>
@@ -1247,19 +1247,19 @@
     <t>Торговцы Артефактами</t>
   </si>
   <si>
-    <t>Колье неприступности</t>
-  </si>
-  <si>
-    <t>Черный рынок</t>
-  </si>
-  <si>
-    <t>Стрелы из Ангельских перьев</t>
-  </si>
-  <si>
-    <t>Нагрудник из серного камня</t>
-  </si>
-  <si>
-    <t>Медаль дипломата</t>
+    <t>Колье Неприступности</t>
+  </si>
+  <si>
+    <t>Черный Рынок</t>
+  </si>
+  <si>
+    <t>Стрелы из Ангельских Перьев</t>
+  </si>
+  <si>
+    <t>Нагрудник из Серного Камня</t>
+  </si>
+  <si>
+    <t>Медаль Дипломата</t>
   </si>
   <si>
     <t>Задание</t>
@@ -1274,7 +1274,7 @@
     <t>Принести ресурсы M5, Золото 9</t>
   </si>
   <si>
-    <t>Монстр Гремлин 8</t>
+    <t>Монстр Гремли 8</t>
   </si>
   <si>
     <t>Заклинание Жажда крови</t>
@@ -1298,7 +1298,7 @@
     <t>341</t>
   </si>
   <si>
-    <t>Артефакт Брелок бесстрастия</t>
+    <t>Артефакт Брелок Бесстрастия</t>
   </si>
   <si>
     <t>Ресурс Золото 6</t>
@@ -1316,7 +1316,7 @@
     <t>Победить героя Амфритрит (66.137.0)</t>
   </si>
   <si>
-    <t>Навык П.Поиск пути</t>
+    <t>Навык П.Поиск Пути</t>
   </si>
   <si>
     <t>Навык A+6</t>
@@ -1325,10 +1325,10 @@
     <t>Мораль +3</t>
   </si>
   <si>
-    <t>Победить монстра Вампир лорд (55.55.0)</t>
-  </si>
-  <si>
-    <t>Принести артефакты Брелок жизни, Брелок абсолютной памяти</t>
+    <t>Победить монстра Вампир Лорд (55.55.0)</t>
+  </si>
+  <si>
+    <t>Принести артефакты Брелок Жизни, Брелок Абсолютной Памяти</t>
   </si>
   <si>
     <t>Принести монстров Крестоносец 4, Цербер 9</t>
@@ -1340,7 +1340,7 @@
     <t>Опыт 1000</t>
   </si>
   <si>
-    <t>Иметь цвет флага Пурпурный</t>
+    <t>Иметь цвет флага Багровый</t>
   </si>
   <si>
     <t>441</t>
@@ -1355,10 +1355,10 @@
     <t>Принести монстров Крестоносец 5, Единорог 8</t>
   </si>
   <si>
-    <t>Принести артефакты Крылья ангела, Колодец волшебника</t>
-  </si>
-  <si>
-    <t>Победить монстра Капитан кентавров (57.75.0)</t>
+    <t>Принести артефакты Крылья Ангела, Колодец Волшебника</t>
+  </si>
+  <si>
+    <t>Победить монстра Капитан Кентавров (57.75.0)</t>
   </si>
   <si>
     <t>Победить героя Катберт (80.134.0)</t>
@@ -1379,13 +1379,13 @@
     <t>Можно забрать</t>
   </si>
   <si>
-    <t>Тяжелый арбалетчик 5, Мечник 8</t>
+    <t>Стрелок 5, Рыцарь 8</t>
   </si>
   <si>
     <t>Оранжевый</t>
   </si>
   <si>
-    <t>Алебардщик 4, Королевский грифон 7</t>
+    <t>Алебардщик 4, Королевский Грифон 7</t>
   </si>
   <si>
     <t>Синий</t>
@@ -1415,7 +1415,7 @@
     <t>Б.Лидерство, Б.Тактика</t>
   </si>
   <si>
-    <t>Копейщик 10, Арбалетчик 5</t>
+    <t>Копейщик 10, Лучник 5</t>
   </si>
   <si>
     <t>Инхам</t>
@@ -1427,7 +1427,7 @@
     <t>Б.Мудрость, Б.Мистицизм</t>
   </si>
   <si>
-    <t>Копейщик 18, Арбалетчик 5</t>
+    <t>Копейщик 18, Лучник 5</t>
   </si>
   <si>
     <t>Сорша</t>
@@ -1436,16 +1436,16 @@
     <t>Б.Лидерство, Б.Нападение</t>
   </si>
   <si>
-    <t>Копейщик 12, Арбалетчик 4</t>
+    <t>Копейщик 12, Лучник 4</t>
   </si>
   <si>
     <t>Валеска</t>
   </si>
   <si>
-    <t>Б.Лидерство, Б.Меткость</t>
-  </si>
-  <si>
-    <t>Арбалетчик 5, Арбалетчик 6</t>
+    <t>Б.Лидерство, Б.Стрельба</t>
+  </si>
+  <si>
+    <t>Лучник 5, Лучник 6</t>
   </si>
   <si>
     <t>Рион</t>
@@ -1457,16 +1457,16 @@
     <t>Копейщик 20, Грифон 3</t>
   </si>
   <si>
-    <t>Палатка первой помощи</t>
+    <t>Санитарная Палатка</t>
   </si>
   <si>
     <t>Катберт</t>
   </si>
   <si>
-    <t>Б.Мудрость, Б.Поместья</t>
-  </si>
-  <si>
-    <t>Копейщик 19, Арбалетчик 5</t>
+    <t>Б.Мудрость, Б.Имущество</t>
+  </si>
+  <si>
+    <t>Копейщик 19, Лучник 5</t>
   </si>
   <si>
     <t>Плата</t>
@@ -1475,10 +1475,10 @@
     <t>Форт на холме</t>
   </si>
   <si>
-    <t>Древо знаний</t>
-  </si>
-  <si>
-    <t>Жертвенный алтарь</t>
+    <t>Древо Знаний</t>
+  </si>
+  <si>
+    <t>Алтарь Жертвоприношиния</t>
   </si>
   <si>
     <t>2000</t>
@@ -1493,16 +1493,16 @@
     <t>Пара</t>
   </si>
   <si>
-    <t>Палатка ключника</t>
+    <t>Палатка Ключника</t>
   </si>
   <si>
     <t>Светло-голубая</t>
   </si>
   <si>
-    <t>Врата подземного мира</t>
-  </si>
-  <si>
-    <t>Двухсторонний монолит</t>
+    <t>Врата Подземного Мира</t>
+  </si>
+  <si>
+    <t>Двухсторонний Монолит</t>
   </si>
   <si>
     <t>2</t>
@@ -1514,10 +1514,10 @@
     <t>1</t>
   </si>
   <si>
-    <t>Монолит входа</t>
-  </si>
-  <si>
-    <t>Монолит выхода</t>
+    <t>Монолит Входа</t>
+  </si>
+  <si>
+    <t>Монолит Выхода</t>
   </si>
   <si>
     <t>День</t>
@@ -1553,13 +1553,13 @@
     <t>Коринф</t>
   </si>
   <si>
-    <t>Темница</t>
+    <t>Подземелье</t>
   </si>
   <si>
     <t>94.108.0</t>
   </si>
   <si>
-    <t>Пурпурный</t>
+    <t>Багровый</t>
   </si>
   <si>
     <t>Спарта</t>
@@ -1571,7 +1571,7 @@
     <t>65.101.0</t>
   </si>
   <si>
-    <t>Красный, Синий, Коричневый, Оранжевый, Пурпурный</t>
+    <t>Красный, Синий, Коричневый, Оранжевый, Багровый</t>
   </si>
   <si>
     <t>S-7</t>
@@ -1598,7 +1598,7 @@
     <t>58.19.0</t>
   </si>
   <si>
-    <t>Бирюзовый</t>
+    <t>Чайный</t>
   </si>
   <si>
     <t>Троя</t>
@@ -1625,7 +1625,7 @@
     <t>Коричневый</t>
   </si>
   <si>
-    <t>Красный, Синий, Оранжевый, Бирюзовый, Розовый</t>
+    <t>Красный, Синий, Оранжевый, Чайный, Розовый</t>
   </si>
   <si>
     <t>Сторожевой пост, Ул.сторожевой пост</t>
@@ -1640,7 +1640,7 @@
     <t>Кузница</t>
   </si>
   <si>
-    <t>Мечник 7</t>
+    <t>Рыцарь 7</t>
   </si>
   <si>
     <t>C-5</t>
@@ -1658,7 +1658,7 @@
     <t>46.101.0</t>
   </si>
   <si>
-    <t>Алебардщик 20, Тяжелый арбалетчик 10, Королевский грифон 5</t>
+    <t>Алебардщик 20, Стрелок 10, Королевский Грифон 5</t>
   </si>
   <si>
     <t>105.92.0</t>
@@ -1670,7 +1670,7 @@
     <t>100.84.0</t>
   </si>
   <si>
-    <t>Б.Лидерство, Б.Защита</t>
+    <t>Б.Лидерство, Б.Доспехи</t>
   </si>
   <si>
     <t>Тиндарей</t>
@@ -1688,7 +1688,7 @@
     <t>Запрещен</t>
   </si>
   <si>
-    <t>Б.Лидерство, Б.Поместья</t>
+    <t>Б.Лидерство, Б.Имущество</t>
   </si>
   <si>
     <t>108.77.0</t>
@@ -1721,7 +1721,7 @@
     <t>Б.Мудрость, Б.Дипломатия</t>
   </si>
   <si>
-    <t>Копейщик 10, Арбалетчик 7</t>
+    <t>Копейщик 10, Лучник 7</t>
   </si>
   <si>
     <t>80.134.0</t>
@@ -1748,22 +1748,22 @@
     <t>112.106.0</t>
   </si>
   <si>
-    <t>Б.Мудрость, Б.Орлиный глаз</t>
-  </si>
-  <si>
-    <t>Снятие заклинания</t>
+    <t>Б.Мудрость, Б.Зоркость</t>
+  </si>
+  <si>
+    <t>Снятие Заклинаний</t>
   </si>
   <si>
     <t>Лоинс</t>
   </si>
   <si>
-    <t>Б.Мудрость, Б.Обучаемость</t>
+    <t>Б.Мудрость, Б.Обучение</t>
   </si>
   <si>
     <t>Молитва</t>
   </si>
   <si>
-    <t>Копейщик 10, Арбалетчик 4</t>
+    <t>Копейщик 10, Лучник 4</t>
   </si>
   <si>
     <t>Каитлин</t>
@@ -1790,7 +1790,7 @@
     <t>Енова</t>
   </si>
   <si>
-    <t>П.Меткость</t>
+    <t>П.Стрельба</t>
   </si>
   <si>
     <t>Роланд</t>
@@ -1814,19 +1814,19 @@
     <t>36.81.0</t>
   </si>
   <si>
-    <t>Б.Меткость, Б.Нападение</t>
-  </si>
-  <si>
-    <t>Капитан кентавров 20, Боевой гном 10, Благородный эльф 5</t>
+    <t>Б.Стрельба, Б.Нападение</t>
+  </si>
+  <si>
+    <t>Капитан Кентавров 20, Боевой Гном 10, Великий Эльф 5</t>
   </si>
   <si>
     <t>Кланси</t>
   </si>
   <si>
-    <t>Б.Сопротивление, Б.Поиск пути</t>
-  </si>
-  <si>
-    <t>Кентавр 13, Гном 5, Лесной эльф 3</t>
+    <t>Б.Сопротивление, Б.Поиск Пути</t>
+  </si>
+  <si>
+    <t>Кентавр 13, Гном 5, Лесной Ельф 3</t>
   </si>
   <si>
     <t>Амфритрит</t>
@@ -1868,7 +1868,7 @@
     <t>Джем</t>
   </si>
   <si>
-    <t>Кентавр 21, Лесной эльф 3</t>
+    <t>Кентавр 21, Лесной Ельф 3</t>
   </si>
   <si>
     <t>Мальком</t>
@@ -1922,10 +1922,10 @@
     <t>Нелла</t>
   </si>
   <si>
-    <t>Б.Грамотность, Б.Защита</t>
-  </si>
-  <si>
-    <t>Гремлин 32, Каменная Горгулья 4</t>
+    <t>Б.Грамотность, Б.Доспехи</t>
+  </si>
+  <si>
+    <t>Гремли 32, Каменная Горгулья 4</t>
   </si>
   <si>
     <t>Торосар</t>
@@ -1940,7 +1940,7 @@
     <t>Б.Грамотность, Б.Сопротивление</t>
   </si>
   <si>
-    <t>Гремлин 34</t>
+    <t>Гремли 34</t>
   </si>
   <si>
     <t>Ризза</t>
@@ -2003,7 +2003,7 @@
     <t>Мариус</t>
   </si>
   <si>
-    <t>П.Защита</t>
+    <t>П.Доспехи</t>
   </si>
   <si>
     <t>Игнат</t>
@@ -2024,7 +2024,7 @@
     <t>Калх</t>
   </si>
   <si>
-    <t>Б.Меткость, Б.Разведка</t>
+    <t>Б.Стрельба, Б.Разведка</t>
   </si>
   <si>
     <t>Пир</t>
@@ -2045,7 +2045,7 @@
     <t>A1-D1-P2-K1</t>
   </si>
   <si>
-    <t>Просмотр земли</t>
+    <t>Просмотр Земли</t>
   </si>
   <si>
     <t>Ксирон</t>
@@ -2090,7 +2090,7 @@
     <t>Моандор</t>
   </si>
   <si>
-    <t>Б.Чародейство, Б.Обучаемость</t>
+    <t>Б.Чародейство, Б.Обучение</t>
   </si>
   <si>
     <t>Чарна</t>
@@ -2108,7 +2108,7 @@
     <t>Б.Чародейство, Б.Нападение</t>
   </si>
   <si>
-    <t>Черт 30, Магог 20, Цербер 10</t>
+    <t>Чёрт 30, Магога 20, Цербер 10</t>
   </si>
   <si>
     <t>Исра</t>
@@ -2123,7 +2123,7 @@
     <t>Галтран</t>
   </si>
   <si>
-    <t>Б.Чародейство, Б.Защита</t>
+    <t>Б.Чародейство, Б.Доспехи</t>
   </si>
   <si>
     <t>Септиенна</t>
@@ -2138,7 +2138,7 @@
     <t>Б.Чародейство, Б.Мудрость</t>
   </si>
   <si>
-    <t>Метеоритный дождь</t>
+    <t>Метеоритный Дождь</t>
   </si>
   <si>
     <t>Сандро</t>
@@ -2153,7 +2153,7 @@
     <t>103.46.1</t>
   </si>
   <si>
-    <t>Б.Чародейство, Б.Орлиный глаз</t>
+    <t>Б.Чародейство, Б.Зоркость</t>
   </si>
   <si>
     <t>Тант</t>
@@ -2162,7 +2162,7 @@
     <t>Б.Чародейство, Б.Мистицизм</t>
   </si>
   <si>
-    <t>Скелет 25, Живой мертвец 4</t>
+    <t>Скелет 25, Живой Мертвец 4</t>
   </si>
   <si>
     <t>Кси</t>
@@ -2210,7 +2210,7 @@
     <t>Б.Лидерство, Б.Сопротивление</t>
   </si>
   <si>
-    <t>Адский троглодит 20, Гарпия-ведьма 10, Злой глаз 5</t>
+    <t>Адский Троглодит 20, Гарпия-Ведьма 10, Дурной Глаз 5</t>
   </si>
   <si>
     <t>Дамакон</t>
@@ -2234,7 +2234,7 @@
     <t>Б.Лидерство, Б.Грамотность</t>
   </si>
   <si>
-    <t>Адский троглодит 50, Гарпия-ведьма 20, Злой глаз 10</t>
+    <t>Адский Троглодит 50, Гарпия-Ведьма 20, Дурной Глаз 10</t>
   </si>
   <si>
     <t>Шакти</t>
@@ -2300,7 +2300,7 @@
     <t>Жабаркас</t>
   </si>
   <si>
-    <t>Б.Нападение, Б.Меткость</t>
+    <t>Б.Нападение, Б.Стрельба</t>
   </si>
   <si>
     <t>Шива</t>
@@ -2312,7 +2312,7 @@
     <t>Гретчин</t>
   </si>
   <si>
-    <t>Б.Нападение, Б.Поиск пути</t>
+    <t>Б.Нападение, Б.Поиск Пути</t>
   </si>
   <si>
     <t>Креллион</t>
@@ -2375,19 +2375,19 @@
     <t>A0-D4-P1-K1</t>
   </si>
   <si>
-    <t>Б.Защита, Б.Сопротивление</t>
+    <t>Б.Доспехи, Б.Сопротивление</t>
   </si>
   <si>
     <t>Дракон</t>
   </si>
   <si>
-    <t>Б.Защита, Б.Лидерство</t>
+    <t>Б.Доспехи, Б.Лидерство</t>
   </si>
   <si>
     <t>Вистан</t>
   </si>
   <si>
-    <t>Б.Защита, Б.Меткость</t>
+    <t>Б.Доспехи, Б.Стрельба</t>
   </si>
   <si>
     <t>Тазар</t>
@@ -2396,25 +2396,25 @@
     <t>Алкин</t>
   </si>
   <si>
-    <t>Б.Защита, Б.Нападение</t>
+    <t>Б.Доспехи, Б.Нападение</t>
   </si>
   <si>
     <t>Корбак</t>
   </si>
   <si>
-    <t>Б.Защита, Б.Поиск пути</t>
+    <t>Б.Доспехи, Б.Поиск Пути</t>
   </si>
   <si>
     <t>Гервульф</t>
   </si>
   <si>
-    <t>Б.Защита, Б.Артиллерия</t>
+    <t>Б.Доспехи, Б.Артиллерия</t>
   </si>
   <si>
     <t>Брохильд</t>
   </si>
   <si>
-    <t>Б.Защита, Б.Разведка</t>
+    <t>Б.Доспехи, Б.Разведка</t>
   </si>
   <si>
     <t>Мирланда</t>
@@ -2447,7 +2447,7 @@
     <t>Тива</t>
   </si>
   <si>
-    <t>Гнолл 10, Ящер 4, Змий 2</t>
+    <t>Гнолл 10, Ящер 4, Змей 2</t>
   </si>
   <si>
     <t>Пасис</t>
@@ -2459,7 +2459,7 @@
     <t>Тунар</t>
   </si>
   <si>
-    <t>Б.Тактика, Б.Поместья</t>
+    <t>Б.Тактика, Б.Имущество</t>
   </si>
   <si>
     <t>Игнисса</t>
@@ -2486,7 +2486,7 @@
     <t>Кальт</t>
   </si>
   <si>
-    <t>Б.Тактика, Б.Обучаемость</t>
+    <t>Б.Тактика, Б.Обучение</t>
   </si>
   <si>
     <t>Луна</t>
@@ -2537,7 +2537,7 @@
     <t>Б.Дипломатия, Б.Лидерство, Б.Нападение</t>
   </si>
   <si>
-    <t>Мастер-гремлин 20, Обсидиановая горгулья 10, Стальной голем 5</t>
+    <t>Мастер-Гремлин 20, Обсидиановая Горгулья 10, Стальной Голем 5</t>
   </si>
   <si>
     <t>Адриэн</t>
@@ -2567,7 +2567,7 @@
     <t>Ксерон</t>
   </si>
   <si>
-    <t>Мантия равновесия</t>
+    <t>Мантия Равновесия</t>
   </si>
   <si>
     <t>Построен</t>
@@ -2591,13 +2591,13 @@
     <t>Благословление, Защита от огня, Каменная кожа, Проклятье, Волшебная стрела, Медлительность</t>
   </si>
   <si>
-    <t>Гремлин 11, Маг 3</t>
-  </si>
-  <si>
-    <t>Удар молнии, Слабость, Стена огня, Защита от воздуха, Ледяная молния</t>
-  </si>
-  <si>
-    <t>Огненный шар, Воздушный щит, Забывчивость, Радость</t>
+    <t>Гремли 11, Маг 3</t>
+  </si>
+  <si>
+    <t>Удар молнии, Слабость, Стена Огня, Защита от воздуха, Ледяная молния</t>
+  </si>
+  <si>
+    <t>Огненный Шар, Воздушный Щит, Забывчивость, Радость</t>
   </si>
   <si>
     <t>Клон, Инферно, Огненный щит</t>
@@ -2630,7 +2630,7 @@
     <t>Затопить корабль, Удар молнии, Разрушающий луч, Ледяная молния, Устранение преград</t>
   </si>
   <si>
-    <t>Огненный шар, Кольцо холода, Минное поле, Радость</t>
+    <t>Огненный Шар, Кольцо холода, Минное поле, Радость</t>
   </si>
   <si>
     <t>Хождение по воде, Городской портал, Молитва</t>
@@ -2642,16 +2642,16 @@
     <t>Winery</t>
   </si>
   <si>
-    <t>Волшебная стрела, Медлительность, Благословление, Ускорение, Снятие заклинания</t>
-  </si>
-  <si>
-    <t>Лесной эльф 5</t>
+    <t>Волшебная стрела, Медлительность, Благословление, Ускорение, Снятие Заклинаний</t>
+  </si>
+  <si>
+    <t>Лесной Ельф 5</t>
   </si>
   <si>
     <t>Разрушающий луч, Точность, Ледяная молния, Удар молнии</t>
   </si>
   <si>
-    <t>Кольцо холода, Воздушный щит, Огненный шар</t>
+    <t>Кольцо холода, Воздушный Щит, Огненный Шар</t>
   </si>
   <si>
     <t>Огненный щит, Инферно</t>
@@ -2660,16 +2660,16 @@
     <t>Волос</t>
   </si>
   <si>
-    <t>Снятие заклинания, Волшебная стрела, Лечение, Щит, Ускорение</t>
+    <t>Снятие Заклинаний, Волшебная стрела, Лечение, Щит, Ускорение</t>
   </si>
   <si>
     <t>Кентавр 10</t>
   </si>
   <si>
-    <t>Стена огня, Ледяная молния, Разрушающий луч, Слепота</t>
-  </si>
-  <si>
-    <t>Огненный шар, Защита от земли, Гипноз</t>
+    <t>Стена Огня, Ледяная молния, Разрушающий луч, Слепота</t>
+  </si>
+  <si>
+    <t>Огненный Шар, Защита от земли, Гипноз</t>
   </si>
   <si>
     <t>Бешенство, Цепная молния</t>
@@ -2681,16 +2681,16 @@
     <t>Иоанна</t>
   </si>
   <si>
-    <t>Ускорение, Каменная кожа, Лечение, Благословление, Снятие заклинания</t>
-  </si>
-  <si>
-    <t>Гарпия 7, Бехолдер 4</t>
-  </si>
-  <si>
-    <t>Удача, Стена огня, Слепота, Ледяная молния</t>
-  </si>
-  <si>
-    <t>Минное поле, Силовое поле, Воздушный щит</t>
+    <t>Ускорение, Каменная кожа, Лечение, Благословление, Снятие Заклинаний</t>
+  </si>
+  <si>
+    <t>Гарпия 7, Созерцатель 4</t>
+  </si>
+  <si>
+    <t>Удача, Стена Огня, Слепота, Ледяная молния</t>
+  </si>
+  <si>
+    <t>Минное поле, Силовое поле, Воздушный Щит</t>
   </si>
   <si>
     <t>Хождение по воде, Восстановление</t>
@@ -2702,25 +2702,25 @@
     <t>Хания</t>
   </si>
   <si>
-    <t>Лечение, Каменная кожа, Волшебная стрела, Вызвать корабль, Медлительность</t>
+    <t>Лечение, Каменная кожа, Волшебная стрела, Вызвать Корабль, Медлительность</t>
   </si>
   <si>
     <t>Ледяная молния, Слепота, Удача, Затопить корабль</t>
   </si>
   <si>
-    <t>Уничтожить нечисть, Забывчивость, Минное поле</t>
+    <t>Уничтожить Нечисть, Забывчивость, Минное поле</t>
   </si>
   <si>
     <t>Контрудар, Восстановление</t>
   </si>
   <si>
-    <t>Вызвать корабль, Волшебная стрела, Жажда крови, Проклятье, Защита от огня</t>
-  </si>
-  <si>
-    <t>Удар молнии, Устранение преград, Точность, Стена огня</t>
-  </si>
-  <si>
-    <t>Воздушный щит, Огненный шар, Минное поле</t>
+    <t>Вызвать Корабль, Волшебная стрела, Жажда крови, Проклятье, Защита от огня</t>
+  </si>
+  <si>
+    <t>Удар молнии, Устранение преград, Точность, Стена Огня</t>
+  </si>
+  <si>
+    <t>Воздушный Щит, Огненный Шар, Минное поле</t>
   </si>
   <si>
     <t>Цепная молния, Восстановление</t>
@@ -2732,13 +2732,13 @@
     <t>Итака</t>
   </si>
   <si>
-    <t>Медлительность, Волшебная стрела, Жажда крови, Ускорение, Снятие заклинания</t>
-  </si>
-  <si>
-    <t>Удар молнии, Маскировка, Зыбучие пески, Стена огня</t>
-  </si>
-  <si>
-    <t>Воздушный щит, Кольцо холода, Неудача</t>
+    <t>Медлительность, Волшебная стрела, Жажда крови, Ускорение, Снятие Заклинаний</t>
+  </si>
+  <si>
+    <t>Удар молнии, Маскировка, Зыбучие пески, Стена Огня</t>
+  </si>
+  <si>
+    <t>Воздушный Щит, Кольцо холода, Неудача</t>
   </si>
   <si>
     <t>Огненный щит, Цепная молния</t>
@@ -2750,7 +2750,7 @@
     <t>Ледяная молния, Удача, Удар молнии, Слабость</t>
   </si>
   <si>
-    <t>Огненный шар, Минное поле, Анти-Магия</t>
+    <t>Огненный Шар, Минное поле, Анти-Магия</t>
   </si>
   <si>
     <t>Печаль, Огненный щит</t>
@@ -2762,13 +2762,13 @@
     <t>Дельфи</t>
   </si>
   <si>
-    <t>Волшебная стрела, Просмотр воздуха, Щит, Вызвать корабль, Снятие заклинания</t>
-  </si>
-  <si>
-    <t>Ледяная молния, Стена огня, Удар молнии, Затопить корабль</t>
-  </si>
-  <si>
-    <t>Уничтожить нечисть, Силовое поле, Огненный шар</t>
+    <t>Волшебная стрела, Просмотр Воздуха, Щит, Вызвать Корабль, Снятие Заклинаний</t>
+  </si>
+  <si>
+    <t>Ледяная молния, Стена Огня, Удар молнии, Затопить корабль</t>
+  </si>
+  <si>
+    <t>Уничтожить Нечисть, Силовое поле, Огненный Шар</t>
   </si>
   <si>
     <t>Берсерк, Восстановление</t>
@@ -2780,22 +2780,22 @@
     <t>Хиос</t>
   </si>
   <si>
-    <t>Лечение, Волшебная стрела, Снятие заклинания, Каменная кожа, Щит</t>
+    <t>Лечение, Волшебная стрела, Снятие Заклинаний, Каменная кожа, Щит</t>
   </si>
   <si>
     <t>Ледяная молния, Зыбучие пески, Разрушающий луч, Точность</t>
   </si>
   <si>
-    <t>Уничтожить нечисть, Кольцо холода, Забывчивость</t>
+    <t>Уничтожить Нечисть, Кольцо холода, Забывчивость</t>
   </si>
   <si>
     <t>Инферно, Хождение по воде</t>
   </si>
   <si>
-    <t>Благословление, Щит, Просмотр воздуха, Просмотр земли, Волшебная стрела</t>
-  </si>
-  <si>
-    <t>Стена огня, Разрушающий луч, Слепота, Ледяная молния</t>
+    <t>Благословление, Щит, Просмотр Воздуха, Просмотр Земли, Волшебная стрела</t>
+  </si>
+  <si>
+    <t>Стена Огня, Разрушающий луч, Слепота, Ледяная молния</t>
   </si>
   <si>
     <t>Защита от земли, Телепорт, Кольцо холода</t>
@@ -2816,22 +2816,22 @@
     <t>Землетрясение, Минное поле, Анти-Магия</t>
   </si>
   <si>
-    <t>Восстановление, Метеоритный дождь</t>
-  </si>
-  <si>
-    <t>Защита от огня, Волшебная стрела, Просмотр земли, Каменная кожа, Благословление</t>
-  </si>
-  <si>
-    <t>Ледяная молния, Видения, Стена огня, Удача</t>
-  </si>
-  <si>
-    <t>Уничтожить нечисть, Кольцо холода, Минное поле</t>
+    <t>Восстановление, Метеоритный Дождь</t>
+  </si>
+  <si>
+    <t>Защита от огня, Волшебная стрела, Просмотр Земли, Каменная кожа, Благословление</t>
+  </si>
+  <si>
+    <t>Ледяная молния, Видения, Стена Огня, Удача</t>
+  </si>
+  <si>
+    <t>Уничтожить Нечисть, Кольцо холода, Минное поле</t>
   </si>
   <si>
     <t>Огненный щит, Клон</t>
   </si>
   <si>
-    <t>Защита от огня, Снятие заклинания, Каменная кожа, Лечение, Благословление</t>
+    <t>Защита от огня, Снятие Заклинаний, Каменная кожа, Лечение, Благословление</t>
   </si>
   <si>
     <t>Разрушающий луч, Удар молнии, Зыбучие пески, Слабость</t>
@@ -2846,10 +2846,10 @@
     <t>Каламата</t>
   </si>
   <si>
-    <t>Волшебная стрела, Благословление, Просмотр воздуха, Лечение, Ускорение</t>
-  </si>
-  <si>
-    <t>Слепота, Удача, Маскировка, Стена огня</t>
+    <t>Волшебная стрела, Благословление, Просмотр Воздуха, Лечение, Ускорение</t>
+  </si>
+  <si>
+    <t>Слепота, Удача, Маскировка, Стена Огня</t>
   </si>
   <si>
     <t>Анти-Магия, Радость, Землетрясение</t>
@@ -2858,37 +2858,37 @@
     <t>Комотини</t>
   </si>
   <si>
-    <t>Каменная кожа, Волшебная стрела, Защита от огня, Ускорение, Вызвать корабль</t>
+    <t>Каменная кожа, Волшебная стрела, Защита от огня, Ускорение, Вызвать Корабль</t>
   </si>
   <si>
     <t>Удача, Ледяная молния, Точность, Маскировка</t>
   </si>
   <si>
-    <t>Огненный шар, Силовое поле, Минное поле</t>
+    <t>Огненный Шар, Силовое поле, Минное поле</t>
   </si>
   <si>
     <t>Берсерк, Армагеддон</t>
   </si>
   <si>
-    <t>Медлительность, Каменная кожа, Защита от воды, Ускорение, Вызвать корабль</t>
+    <t>Медлительность, Каменная кожа, Защита от воды, Ускорение, Вызвать Корабль</t>
   </si>
   <si>
     <t>Удача, Разрушающий луч, Ледяная молния, Слепота</t>
   </si>
   <si>
-    <t>Защита от земли, Огненный шар, Кольцо холода</t>
-  </si>
-  <si>
-    <t>Метеоритный дождь, Палач</t>
-  </si>
-  <si>
-    <t>Волшебная стрела, Жажда крови, Медлительность, Лечение, Просмотр земли</t>
-  </si>
-  <si>
-    <t>Видения, Стена огня, Удар молнии, Точность</t>
-  </si>
-  <si>
-    <t>Минное поле, Огненный шар, Забывчивость</t>
+    <t>Защита от земли, Огненный Шар, Кольцо холода</t>
+  </si>
+  <si>
+    <t>Метеоритный Дождь, Палач</t>
+  </si>
+  <si>
+    <t>Волшебная стрела, Жажда крови, Медлительность, Лечение, Просмотр Земли</t>
+  </si>
+  <si>
+    <t>Видения, Стена Огня, Удар молнии, Точность</t>
+  </si>
+  <si>
+    <t>Минное поле, Огненный Шар, Забывчивость</t>
   </si>
   <si>
     <t>Палач, Городской портал</t>
@@ -2897,19 +2897,19 @@
     <t>Летний Домик</t>
   </si>
   <si>
-    <t>Лечение, Волшебная стрела, Ускорение, Снятие заклинания, Жажда крови</t>
+    <t>Лечение, Волшебная стрела, Ускорение, Снятие Заклинаний, Жажда крови</t>
   </si>
   <si>
     <t>Удар молнии, Защита от воздуха, Слабость, Разрушающий луч</t>
   </si>
   <si>
-    <t>Землетрясение, Огненный шар, Телепорт</t>
+    <t>Землетрясение, Огненный Шар, Телепорт</t>
   </si>
   <si>
     <t>Инферно, Берсерк</t>
   </si>
   <si>
-    <t>Огненный Элементаль</t>
+    <t>Огенный Элементаль</t>
   </si>
   <si>
     <t>Кукла</t>
@@ -2924,19 +2924,19 @@
     <t>Циклоп 2</t>
   </si>
   <si>
-    <t>Вампир лорд 11</t>
+    <t>Вампир Лорд 11</t>
   </si>
   <si>
     <t>Ноги</t>
   </si>
   <si>
-    <t>Хижина провидца</t>
-  </si>
-  <si>
-    <t>Красный дракон 8</t>
-  </si>
-  <si>
-    <t>Воздушный элементаль 10</t>
+    <t>Хижина Провидца</t>
+  </si>
+  <si>
+    <t>Красный Дракон 8</t>
+  </si>
+  <si>
+    <t>Воздушный Элементаль 10</t>
   </si>
   <si>
     <t>Крестоносец 10</t>
@@ -2945,7 +2945,7 @@
     <t>Городок</t>
   </si>
   <si>
-    <t>Воздушный щит</t>
+    <t>Воздушный Щит</t>
   </si>
   <si>
     <t>Клон</t>
@@ -2993,7 +2993,7 @@
     <t>Вода</t>
   </si>
   <si>
-    <t>Меткость</t>
+    <t>Стрельба</t>
   </si>
   <si>
     <t>Воздух</t>
@@ -3002,19 +3002,19 @@
     <t>∑ XP</t>
   </si>
   <si>
-    <t>Королева медуза 14</t>
-  </si>
-  <si>
-    <t>Камень знаний</t>
-  </si>
-  <si>
-    <t>Магический элементаль 8</t>
-  </si>
-  <si>
-    <t>Змий-дракон 16</t>
-  </si>
-  <si>
-    <t>Дендроид охранник 12</t>
+    <t>Королева Медуза 14</t>
+  </si>
+  <si>
+    <t>Камень Знаний</t>
+  </si>
+  <si>
+    <t>Магический Элементаль 8</t>
+  </si>
+  <si>
+    <t>Стрекоза 16</t>
+  </si>
+  <si>
+    <t>Дендроид Охранник 12</t>
   </si>
   <si>
     <t>Орк 14</t>
@@ -3023,28 +3023,28 @@
     <t>Налетчик 24</t>
   </si>
   <si>
-    <t>Элементаль воды 14</t>
-  </si>
-  <si>
-    <t>Ящер-воин 22</t>
-  </si>
-  <si>
-    <t>Змий 11</t>
-  </si>
-  <si>
-    <t>Змий 20</t>
-  </si>
-  <si>
-    <t>Ледяной элементаль 17</t>
-  </si>
-  <si>
-    <t>Адская гончая 20</t>
+    <t>Элементаль Воды 14</t>
+  </si>
+  <si>
+    <t>Ящер-Воин 22</t>
+  </si>
+  <si>
+    <t>Змей 11</t>
+  </si>
+  <si>
+    <t>Змей 20</t>
+  </si>
+  <si>
+    <t>Ледяной Элементаль 17</t>
+  </si>
+  <si>
+    <t>Адская Гончая 20</t>
   </si>
   <si>
     <t>Ящер 21</t>
   </si>
   <si>
-    <t>Каменный голем 17</t>
+    <t>Каменный Голем 17</t>
   </si>
   <si>
     <t>Вор 26</t>
@@ -3056,22 +3056,22 @@
     <t>Наездник на волках 23</t>
   </si>
   <si>
-    <t>Фабрика големов</t>
-  </si>
-  <si>
-    <t>Золотой голем 9, Алмазный голем 6</t>
+    <t>Фабрика Големов</t>
+  </si>
+  <si>
+    <t>Золотой Голем 9, Алмазный Голем 6</t>
   </si>
   <si>
     <t>Гарпия 28</t>
   </si>
   <si>
-    <t>Тяжелый арбалетчик 21</t>
-  </si>
-  <si>
-    <t>Орк-вождь 15</t>
-  </si>
-  <si>
-    <t>Огненный элементаль 21</t>
+    <t>Стрелок 21</t>
+  </si>
+  <si>
+    <t>Орк-Вождь 15</t>
+  </si>
+  <si>
+    <t>Огненный Элементаль 21</t>
   </si>
   <si>
     <t>Крестоносец 14</t>
@@ -3083,22 +3083,22 @@
     <t>Ящер 27</t>
   </si>
   <si>
-    <t>Злой глаз 15</t>
+    <t>Дурной Глаз 15</t>
   </si>
   <si>
     <t>Мумия 17</t>
   </si>
   <si>
-    <t>Элементаль воды 24</t>
-  </si>
-  <si>
-    <t>Лесной эльф 20</t>
-  </si>
-  <si>
-    <t>Вампир лорд 10</t>
-  </si>
-  <si>
-    <t>Королева медуза 12</t>
+    <t>Элементаль Воды 24</t>
+  </si>
+  <si>
+    <t>Лесной Ельф 20</t>
+  </si>
+  <si>
+    <t>Вампир Лорд 10</t>
+  </si>
+  <si>
+    <t>Королева Медуза 12</t>
   </si>
   <si>
     <t>Демон 18</t>
@@ -3107,43 +3107,43 @@
     <t>Гидра 9</t>
   </si>
   <si>
-    <t>Королева медуза 11</t>
-  </si>
-  <si>
-    <t>Разлом элементалей земли</t>
-  </si>
-  <si>
-    <t>Элементаль земли 12</t>
-  </si>
-  <si>
-    <t>Опушка единорогов</t>
+    <t>Королева Медуза 11</t>
+  </si>
+  <si>
+    <t>Разлом Элементалей Земли</t>
+  </si>
+  <si>
+    <t>Элементаль Земли 12</t>
+  </si>
+  <si>
+    <t>Опушка Единорогов</t>
   </si>
   <si>
     <t>Единорог 6</t>
   </si>
   <si>
-    <t>Лесной эльф 24</t>
-  </si>
-  <si>
-    <t>Утес драконов</t>
-  </si>
-  <si>
-    <t>Зеленый дракон 3</t>
-  </si>
-  <si>
-    <t>Каменный голем 23</t>
-  </si>
-  <si>
-    <t>Пещера драконов</t>
-  </si>
-  <si>
-    <t>Красный дракон 3</t>
+    <t>Лесной Ельф 24</t>
+  </si>
+  <si>
+    <t>Утес Драконов</t>
+  </si>
+  <si>
+    <t>Зеленый Дракон 3</t>
+  </si>
+  <si>
+    <t>Каменный Голем 23</t>
+  </si>
+  <si>
+    <t>Пещера Драконов</t>
+  </si>
+  <si>
+    <t>Красный Дракон 3</t>
   </si>
   <si>
     <t>Вампир 15</t>
   </si>
   <si>
-    <t>Элементаль земли 30</t>
+    <t>Элементаль Земли 30</t>
   </si>
   <si>
     <t>Циклоп 12</t>
@@ -3152,25 +3152,25 @@
     <t>Копейщик 44</t>
   </si>
   <si>
-    <t>Воздушный элементаль 9</t>
-  </si>
-  <si>
-    <t>Капитан кентавров 21</t>
+    <t>Воздушный Элементаль 9</t>
+  </si>
+  <si>
+    <t>Капитан Кентавров 21</t>
   </si>
   <si>
     <t>Грифон 13</t>
   </si>
   <si>
-    <t>Вампир лорд 12</t>
-  </si>
-  <si>
-    <t>Арбалетчик 27</t>
-  </si>
-  <si>
-    <t>Живой мертвец 21</t>
-  </si>
-  <si>
-    <t>Элементаль воды 23</t>
+    <t>Вампир Лорд 12</t>
+  </si>
+  <si>
+    <t>Лучник 27</t>
+  </si>
+  <si>
+    <t>Живой Мертвец 21</t>
+  </si>
+  <si>
+    <t>Элементаль Воды 23</t>
   </si>
   <si>
     <t>Фея 26</t>
@@ -3179,28 +3179,28 @@
     <t>Горгона 24</t>
   </si>
   <si>
-    <t>Архи-маг 15</t>
-  </si>
-  <si>
-    <t>Лесной эльф 16</t>
+    <t>Архи-Маг 15</t>
+  </si>
+  <si>
+    <t>Лесной Ельф 16</t>
   </si>
   <si>
     <t>Фанатик 11</t>
   </si>
   <si>
-    <t>Ящер-воин 25</t>
+    <t>Ящер-Воин 25</t>
   </si>
   <si>
     <t>Наездник на волках 20</t>
   </si>
   <si>
-    <t>Змий 12</t>
+    <t>Змей 12</t>
   </si>
   <si>
     <t>Грифон 19</t>
   </si>
   <si>
-    <t>Серебряный пегас 14</t>
+    <t>Серебрянный Пегас 14</t>
   </si>
   <si>
     <t>Вор 24</t>
@@ -3209,25 +3209,25 @@
     <t>Зомби 23</t>
   </si>
   <si>
-    <t>Огр-шаман 10</t>
-  </si>
-  <si>
-    <t>Благородный эльф 20</t>
-  </si>
-  <si>
-    <t>Арка дендроидов</t>
-  </si>
-  <si>
-    <t>Дендроид охранник 9</t>
-  </si>
-  <si>
-    <t>Вампир лорд 16</t>
+    <t>Людоед Маг 10</t>
+  </si>
+  <si>
+    <t>Великий Эльф 20</t>
+  </si>
+  <si>
+    <t>Арка Дендроидов</t>
+  </si>
+  <si>
+    <t>Дендроид Охранник 9</t>
+  </si>
+  <si>
+    <t>Вампир Лорд 16</t>
   </si>
   <si>
     <t>Кентавр 32</t>
   </si>
   <si>
-    <t>Капитан кентавров 26</t>
+    <t>Капитан Кентавров 26</t>
   </si>
   <si>
     <t>Грифон 21</t>
@@ -3236,19 +3236,19 @@
     <t>Вампир 20</t>
   </si>
   <si>
-    <t>Королевский грифон 12</t>
-  </si>
-  <si>
-    <t>Гремлин 37</t>
-  </si>
-  <si>
-    <t>Огненный элементаль 23</t>
-  </si>
-  <si>
-    <t>Боевой гном 16</t>
-  </si>
-  <si>
-    <t>Змий-дракон 11</t>
+    <t>Королевский Грифон 12</t>
+  </si>
+  <si>
+    <t>Гремли 37</t>
+  </si>
+  <si>
+    <t>Огненный Элементаль 23</t>
+  </si>
+  <si>
+    <t>Боевой Гном 16</t>
+  </si>
+  <si>
+    <t>Стрекоза 11</t>
   </si>
   <si>
     <t>Вор 23</t>
@@ -3272,16 +3272,16 @@
     <t>Мумия 18</t>
   </si>
   <si>
-    <t>Великий василиск 8</t>
-  </si>
-  <si>
-    <t>Бехолдер 18</t>
-  </si>
-  <si>
-    <t>Магог 24</t>
-  </si>
-  <si>
-    <t>Королевский грифон 19</t>
+    <t>Великий Василиск 8</t>
+  </si>
+  <si>
+    <t>Созерцатель 18</t>
+  </si>
+  <si>
+    <t>Магога 24</t>
+  </si>
+  <si>
+    <t>Королевский Грифон 19</t>
   </si>
   <si>
     <t>Налетчик 18</t>
@@ -3290,34 +3290,34 @@
     <t>Гоблин 46</t>
   </si>
   <si>
-    <t>Живой мертвец 20</t>
+    <t>Живой Мертвец 20</t>
   </si>
   <si>
     <t>Гарпия 22</t>
   </si>
   <si>
-    <t>Гнолл-мародер 26</t>
-  </si>
-  <si>
-    <t>Боевой гном 25</t>
+    <t>Гнолл-Мародер 26</t>
+  </si>
+  <si>
+    <t>Боевой Гном 25</t>
   </si>
   <si>
     <t>Крестоносец 13</t>
   </si>
   <si>
-    <t>Обсидиановая горгулья 23</t>
-  </si>
-  <si>
-    <t>Маленькая фея 28</t>
-  </si>
-  <si>
-    <t>Порождение зла 10</t>
-  </si>
-  <si>
-    <t>Гнолл-мародер 22</t>
-  </si>
-  <si>
-    <t>Боевой гном 19</t>
+    <t>Обсидиановая Горгулья 23</t>
+  </si>
+  <si>
+    <t>Маленькая Фея 28</t>
+  </si>
+  <si>
+    <t>Порождение Зла 10</t>
+  </si>
+  <si>
+    <t>Гнолл-Мародер 22</t>
+  </si>
+  <si>
+    <t>Боевой Гном 19</t>
   </si>
   <si>
     <t>Фея 20</t>
@@ -3326,28 +3326,28 @@
     <t>Цербер 15</t>
   </si>
   <si>
-    <t>Дендроид солдат 12</t>
-  </si>
-  <si>
-    <t>Мечник 12</t>
-  </si>
-  <si>
-    <t>Королевский грифон 13</t>
-  </si>
-  <si>
-    <t>Элементаль шторма 6</t>
-  </si>
-  <si>
-    <t>Ящер-воин 24</t>
-  </si>
-  <si>
-    <t>Черт 30</t>
-  </si>
-  <si>
-    <t>Змий 17</t>
-  </si>
-  <si>
-    <t>Гарпия-ведьма 21</t>
+    <t>Дендроид Солдат 12</t>
+  </si>
+  <si>
+    <t>Рыцарь 12</t>
+  </si>
+  <si>
+    <t>Королевский Грифон 13</t>
+  </si>
+  <si>
+    <t>Элементаль Шторма 6</t>
+  </si>
+  <si>
+    <t>Ящер-Воин 24</t>
+  </si>
+  <si>
+    <t>Чёрт 30</t>
+  </si>
+  <si>
+    <t>Змей 17</t>
+  </si>
+  <si>
+    <t>Гарпия-Ведьма 21</t>
   </si>
   <si>
     <t>Ящер 30</t>
@@ -3359,7 +3359,7 @@
     <t>Каменная Горгулья 19</t>
   </si>
   <si>
-    <t>Орк на кабане 18</t>
+    <t>Кабан 18</t>
   </si>
   <si>
     <t>Кочевник 12</t>
@@ -3368,7 +3368,7 @@
     <t>Страж 23</t>
   </si>
   <si>
-    <t>Гарпия-ведьма 17</t>
+    <t>Гарпия-Ведьма 17</t>
   </si>
   <si>
     <t>Зомби 19</t>
@@ -3377,13 +3377,13 @@
     <t>Гном 22</t>
   </si>
   <si>
-    <t>Гремлин 20</t>
-  </si>
-  <si>
-    <t>Благородный эльф 15</t>
-  </si>
-  <si>
-    <t>Злой глаз 12</t>
+    <t>Гремли 20</t>
+  </si>
+  <si>
+    <t>Великий Эльф 15</t>
+  </si>
+  <si>
+    <t>Дурной Глаз 12</t>
   </si>
   <si>
     <t>Скелет 30</t>
@@ -3398,16 +3398,16 @@
     <t>Мумия 16</t>
   </si>
   <si>
-    <t>Бехолдер 24</t>
-  </si>
-  <si>
-    <t>Золотой голем 15</t>
+    <t>Созерцатель 24</t>
+  </si>
+  <si>
+    <t>Золотой Голем 15</t>
   </si>
   <si>
     <t>Фанатик 8</t>
   </si>
   <si>
-    <t>Ледяной элементаль 19</t>
+    <t>Ледяной Элементаль 19</t>
   </si>
   <si>
     <t>Мумия 15</t>
@@ -3419,49 +3419,49 @@
     <t>Минотавр 10</t>
   </si>
   <si>
-    <t>Рыцарь смерти 8</t>
+    <t>Рыцарь Смерти 8</t>
   </si>
   <si>
     <t>Нага 5</t>
   </si>
   <si>
-    <t>Могущественный лич 10</t>
+    <t>Могущественный Лич 10</t>
   </si>
   <si>
     <t>Налетчик 25</t>
   </si>
   <si>
-    <t>Дракон-привидение 4</t>
-  </si>
-  <si>
-    <t>Воин скелет 26</t>
-  </si>
-  <si>
-    <t>Архи-маг 14</t>
-  </si>
-  <si>
-    <t>Капитан кентавров 30</t>
-  </si>
-  <si>
-    <t>Боевой гном 18</t>
+    <t>Дракон-Привидение 4</t>
+  </si>
+  <si>
+    <t>Воин Скелет 26</t>
+  </si>
+  <si>
+    <t>Архи-Маг 14</t>
+  </si>
+  <si>
+    <t>Капитан Кентавров 30</t>
+  </si>
+  <si>
+    <t>Боевой Гном 18</t>
   </si>
   <si>
     <t>Налетчик 16</t>
   </si>
   <si>
-    <t>Элементаль воды 13</t>
-  </si>
-  <si>
-    <t>Тяжелый арбалетчик 19</t>
+    <t>Элементаль Воды 13</t>
+  </si>
+  <si>
+    <t>Стрелок 19</t>
   </si>
   <si>
     <t>Лич 13</t>
   </si>
   <si>
-    <t>Мастер-джинн 8</t>
-  </si>
-  <si>
-    <t>Элементаль земли 20</t>
+    <t>Мастер-Джин 8</t>
+  </si>
+  <si>
+    <t>Элементаль Земли 20</t>
   </si>
   <si>
     <t>Крестоносец 12</t>
@@ -3470,10 +3470,10 @@
     <t>Чемпион 10</t>
   </si>
   <si>
-    <t>Воин скелет 22</t>
-  </si>
-  <si>
-    <t>Костяной дракон 10</t>
+    <t>Воин Скелет 22</t>
+  </si>
+  <si>
+    <t>Костяной Дракон 10</t>
   </si>
   <si>
     <t>Страж 16</t>
@@ -3485,10 +3485,10 @@
     <t>Скелет 50</t>
   </si>
   <si>
-    <t>Черт 22</t>
-  </si>
-  <si>
-    <t>Воин скелет 23</t>
+    <t>Чёрт 22</t>
+  </si>
+  <si>
+    <t>Воин Скелет 23</t>
   </si>
   <si>
     <t>Крестоносец 16</t>
@@ -3503,16 +3503,16 @@
     <t>Привидение 15</t>
   </si>
   <si>
-    <t>Живой мертвец 30</t>
-  </si>
-  <si>
-    <t>Змий 18</t>
+    <t>Живой Мертвец 30</t>
+  </si>
+  <si>
+    <t>Змей 18</t>
   </si>
   <si>
     <t>Наездник на волках 27</t>
   </si>
   <si>
-    <t>Тяжелый арбалетчик 16</t>
+    <t>Стрелок 16</t>
   </si>
   <si>
     <t>Медуза 13</t>
@@ -3527,7 +3527,7 @@
     <t>Цербер 16</t>
   </si>
   <si>
-    <t>Джинн 14</t>
+    <t>Джин 14</t>
   </si>
   <si>
     <t>Привидение 1000</t>
@@ -3539,28 +3539,28 @@
     <t>Маг 10</t>
   </si>
   <si>
-    <t>Могущественный лич 11</t>
-  </si>
-  <si>
-    <t>Вампир лорд 13</t>
+    <t>Могущественный Лич 11</t>
+  </si>
+  <si>
+    <t>Вампир Лорд 13</t>
   </si>
   <si>
     <t>Привидение 16</t>
   </si>
   <si>
-    <t>Воин скелет 21</t>
+    <t>Воин Скелет 21</t>
   </si>
   <si>
     <t>Страж 14</t>
   </si>
   <si>
-    <t>Энергетический элементаль 25</t>
+    <t>Энергетический Элементаль 25</t>
   </si>
   <si>
     <t>Монах 12</t>
   </si>
   <si>
-    <t>Король минотавр 12</t>
+    <t>Король Минотавр 12</t>
   </si>
   <si>
     <t>Грифон 15</t>
@@ -3569,25 +3569,25 @@
     <t>Чемпион 7</t>
   </si>
   <si>
-    <t>Лесной эльф 18</t>
-  </si>
-  <si>
-    <t>Ящер-воин 16</t>
+    <t>Лесной Ельф 18</t>
+  </si>
+  <si>
+    <t>Ящер-Воин 16</t>
   </si>
   <si>
     <t>Минотавр 11</t>
   </si>
   <si>
-    <t>Змий-дракон 10</t>
-  </si>
-  <si>
-    <t>Воздушный элементаль 11</t>
-  </si>
-  <si>
-    <t>Злой глаз 13</t>
-  </si>
-  <si>
-    <t>Змий 10</t>
+    <t>Стрекоза 10</t>
+  </si>
+  <si>
+    <t>Воздушный Элементаль 11</t>
+  </si>
+  <si>
+    <t>Дурной Глаз 13</t>
+  </si>
+  <si>
+    <t>Змей 10</t>
   </si>
   <si>
     <t>Демон 13</t>
@@ -3596,10 +3596,10 @@
     <t>Маг 19</t>
   </si>
   <si>
-    <t>Змий-дракон 12</t>
-  </si>
-  <si>
-    <t>Элементаль шторма 10</t>
+    <t>Стрекоза 12</t>
+  </si>
+  <si>
+    <t>Элементаль Шторма 10</t>
   </si>
   <si>
     <t>Гном 20</t>
@@ -3611,28 +3611,28 @@
     <t>Ящер 26</t>
   </si>
   <si>
-    <t>Каменный голем 16</t>
-  </si>
-  <si>
-    <t>Элементаль магмы 18</t>
+    <t>Каменный Голем 16</t>
+  </si>
+  <si>
+    <t>Элементаль Магмы 18</t>
   </si>
   <si>
     <t>Привидение 18</t>
   </si>
   <si>
-    <t>Злой глаз 19</t>
-  </si>
-  <si>
-    <t>Стальной голем 15</t>
-  </si>
-  <si>
-    <t>Элементаль воды 15</t>
+    <t>Дурной Глаз 19</t>
+  </si>
+  <si>
+    <t>Стальной Голем 15</t>
+  </si>
+  <si>
+    <t>Элементаль Воды 15</t>
   </si>
   <si>
     <t>Грифон 25</t>
   </si>
   <si>
-    <t>Великий василиск 9</t>
+    <t>Великий Василиск 9</t>
   </si>
   <si>
     <t>Тренировочная площадка</t>
@@ -3641,16 +3641,16 @@
     <t>Кавалерист 6</t>
   </si>
   <si>
-    <t>Боевой гном 23</t>
+    <t>Боевой Гном 23</t>
   </si>
   <si>
     <t>Вор 19</t>
   </si>
   <si>
-    <t>Магог 21</t>
-  </si>
-  <si>
-    <t>Орк-вождь 12</t>
+    <t>Магога 21</t>
+  </si>
+  <si>
+    <t>Орк-Вождь 12</t>
   </si>
 </sst>
 </file>
@@ -43878,16 +43878,16 @@
         <v>441</v>
       </c>
       <c r="E387" t="s">
-        <v>361</v>
+        <v>289</v>
       </c>
       <c r="F387">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G387" t="s">
-        <v>509</v>
+        <v>496</v>
       </c>
       <c r="K387" t="s">
-        <v>621</v>
+        <v>589</v>
       </c>
       <c r="L387" t="s">
         <v>548</v>
@@ -43898,16 +43898,16 @@
         <v>441</v>
       </c>
       <c r="E388" t="s">
-        <v>366</v>
+        <v>563</v>
       </c>
       <c r="F388">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G388" t="s">
-        <v>509</v>
+        <v>267</v>
       </c>
       <c r="K388" t="s">
-        <v>628</v>
+        <v>561</v>
       </c>
       <c r="L388" t="s">
         <v>548</v>
@@ -43918,16 +43918,16 @@
         <v>441</v>
       </c>
       <c r="E389" t="s">
-        <v>563</v>
+        <v>351</v>
       </c>
       <c r="F389">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G389" t="s">
-        <v>267</v>
+        <v>440</v>
       </c>
       <c r="K389" t="s">
-        <v>561</v>
+        <v>547</v>
       </c>
       <c r="L389" t="s">
         <v>548</v>
@@ -43938,7 +43938,7 @@
         <v>441</v>
       </c>
       <c r="E390" t="s">
-        <v>351</v>
+        <v>363</v>
       </c>
       <c r="F390">
         <v>1</v>
@@ -43947,7 +43947,7 @@
         <v>440</v>
       </c>
       <c r="K390" t="s">
-        <v>547</v>
+        <v>791</v>
       </c>
       <c r="L390" t="s">
         <v>548</v>
@@ -43958,16 +43958,16 @@
         <v>441</v>
       </c>
       <c r="E391" t="s">
-        <v>363</v>
+        <v>356</v>
       </c>
       <c r="F391">
         <v>1</v>
       </c>
       <c r="G391" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="K391" t="s">
-        <v>791</v>
+        <v>598</v>
       </c>
       <c r="L391" t="s">
         <v>548</v>
@@ -43978,16 +43978,16 @@
         <v>441</v>
       </c>
       <c r="E392" t="s">
-        <v>356</v>
+        <v>346</v>
       </c>
       <c r="F392">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G392" t="s">
         <v>437</v>
       </c>
       <c r="K392" t="s">
-        <v>598</v>
+        <v>695</v>
       </c>
       <c r="L392" t="s">
         <v>548</v>
@@ -43998,16 +43998,16 @@
         <v>441</v>
       </c>
       <c r="E393" t="s">
-        <v>346</v>
+        <v>611</v>
       </c>
       <c r="F393">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G393" t="s">
-        <v>437</v>
+        <v>512</v>
       </c>
       <c r="K393" t="s">
-        <v>695</v>
+        <v>616</v>
       </c>
       <c r="L393" t="s">
         <v>548</v>
@@ -44018,16 +44018,16 @@
         <v>441</v>
       </c>
       <c r="E394" t="s">
-        <v>289</v>
+        <v>361</v>
       </c>
       <c r="F394">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G394" t="s">
-        <v>496</v>
+        <v>509</v>
       </c>
       <c r="K394" t="s">
-        <v>589</v>
+        <v>621</v>
       </c>
       <c r="L394" t="s">
         <v>548</v>
@@ -44038,16 +44038,16 @@
         <v>441</v>
       </c>
       <c r="E395" t="s">
-        <v>611</v>
+        <v>366</v>
       </c>
       <c r="F395">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G395" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
       <c r="K395" t="s">
-        <v>616</v>
+        <v>628</v>
       </c>
       <c r="L395" t="s">
         <v>548</v>
